--- a/public/assets/educacao.xlsx
+++ b/public/assets/educacao.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Major</t>
   </si>
@@ -52,26 +52,32 @@
     <t>2025 - Presente</t>
   </si>
   <si>
+    <t>https://graduacao.unilasalle.edu.br/cursos-ead/analise-e-desenvolvimento-de-sistemas</t>
+  </si>
+  <si>
     <t>unilasalle.jpg</t>
   </si>
   <si>
-    <t>Bacharelado em Serviço Social</t>
-  </si>
-  <si>
-    <t>UFRGS (Universidade Federal do Rio Grande do Sul)</t>
-  </si>
-  <si>
-    <t>http://www.ufrgs.br/ufrgs/ensino/graduacao/cursos/exibeCurso?cod_curso=907</t>
-  </si>
-  <si>
-    <t>ufrgs.jpg</t>
+    <t>Bacharelado em Ciência da Computação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unisinos </t>
+  </si>
+  <si>
+    <t>2026 - Presente</t>
+  </si>
+  <si>
+    <t>https://www.unisinos.br/graduacao/ciencia-da-computacao/porto-alegre</t>
+  </si>
+  <si>
+    <t>unisinos.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -85,6 +91,11 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -107,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -122,6 +133,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -133,6 +147,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -380,28 +398,28 @@
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/educacao.xlsx
+++ b/public/assets/educacao.xlsx
@@ -11,27 +11,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Major</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t>School</t>
   </si>
   <si>
+    <t>City</t>
+  </si>
+  <si>
     <t>Time</t>
   </si>
   <si>
     <t>Link</t>
   </si>
   <si>
+    <t>Desc</t>
+  </si>
+  <si>
     <t>Image</t>
   </si>
   <si>
-    <t>Técnico em Desenvolvimento de Sistemas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFRS (Instituto Federal de Educação, Ciência e Tecnologia)  </t>
+    <t>Desenvolvimento de Sistemas</t>
+  </si>
+  <si>
+    <t>Técnico</t>
+  </si>
+  <si>
+    <t>IFRS</t>
+  </si>
+  <si>
+    <t>Canoas, RS</t>
   </si>
   <si>
     <t>2019 - 2022</t>
@@ -40,10 +55,16 @@
     <t>https://ifrs.edu.br/canoas/no-campus/cursos/curso-tecnico-em-desenvolvimento-de-sistemas-integrado-ao-ensino-medio/</t>
   </si>
   <si>
+    <t>Formação focada no desenvolvimento de sistemas, abrangendo lógica de programação, banco de dados e diversas linguagens para o mercado. O curso une o ensino médio à prática técnica, preparando o aluno para projetar e manter soluções computacionais completas.</t>
+  </si>
+  <si>
     <t>ifrs.jpeg</t>
   </si>
   <si>
-    <t>Tecnólogo em Análise e Desenvolvimento de Sistemas</t>
+    <t>Análise e Desenvolvimento de Sistemas</t>
+  </si>
+  <si>
+    <t>Tecnólogo</t>
   </si>
   <si>
     <t>Universidade La Salle</t>
@@ -55,19 +76,31 @@
     <t>https://graduacao.unilasalle.edu.br/cursos-ead/analise-e-desenvolvimento-de-sistemas</t>
   </si>
   <si>
+    <t>Foco no ciclo de vida do software, desde a análise de requisitos até a manutenção e gestão de dados. Prepara o aluno para criar soluções tecnológicas inovadoras com foco prático e rápido para as demandas do mercado.</t>
+  </si>
+  <si>
     <t>unilasalle.jpg</t>
   </si>
   <si>
-    <t>Bacharelado em Ciência da Computação</t>
+    <t>Ciência da Computação</t>
+  </si>
+  <si>
+    <t>Bacharelado</t>
   </si>
   <si>
     <t xml:space="preserve">Unisinos </t>
   </si>
   <si>
+    <t>Porto Alegre, RS</t>
+  </si>
+  <si>
     <t>2026 - Presente</t>
   </si>
   <si>
     <t>https://www.unisinos.br/graduacao/ciencia-da-computacao/porto-alegre</t>
+  </si>
+  <si>
+    <t>Formação sólida em fundamentos teóricos e práticos, abrangendo Inteligência Artificial, Ciência de Dados e sistemas complexos. Incentiva a pesquisa, a criatividade e a resolução de problemas de alto nível técnico em ambientes de simulação e inovação.</t>
   </si>
   <si>
     <t>unisinos.jpg</t>
@@ -77,7 +110,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -96,6 +129,10 @@
     <font>
       <u/>
       <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -118,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -135,6 +172,12 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -364,69 +407,105 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
+      <c r="E3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="D2"/>
-    <hyperlink r:id="rId2" ref="D3"/>
-    <hyperlink r:id="rId3" ref="D4"/>
+    <hyperlink r:id="rId1" ref="F2"/>
+    <hyperlink r:id="rId2" ref="F3"/>
+    <hyperlink r:id="rId3" ref="F4"/>
   </hyperlinks>
   <drawing r:id="rId4"/>
 </worksheet>
